--- a/Front_Extended/Front_Extended_Front/Release/PCBA/02.BOM/Bill_Of_Materials-BoM(Main).xlsx
+++ b/Front_Extended/Front_Extended_Front/Release/PCBA/02.BOM/Bill_Of_Materials-BoM(Main).xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JustinKim\Desktop\src_moddo\moddoMOUSE-PCB\Front_Extended\Front_Extended_Front\Release\PCBA\02.BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JK\Desktop\src_moddo\moddoMOUSE-PCB\Front_Extended\Front_Extended_Front\Release\PCBA\02.BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1E9F4C7D-7F4E-4679-8D6B-7DFE3D536A72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3901569F-D329-4B2A-98D0-DE6A39E23565}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-51720" yWindow="30" windowWidth="51840" windowHeight="21120" xr2:uid="{113F4B74-E6C0-4256-AF18-584A6A681927}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="61656" windowHeight="16776" xr2:uid="{1DCE6AF1-80F7-459C-B90B-D84B2D275F5E}"/>
   </bookViews>
   <sheets>
     <sheet name="Bill_Of_Materials-BoM(Main)" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="38">
   <si>
     <t>Designator</t>
   </si>
@@ -95,19 +95,13 @@
     <t>EC10E1220501</t>
   </si>
   <si>
-    <t>Rotary Encoder Mechanical 12 Quadrature (Incremental) Vertical</t>
-  </si>
-  <si>
-    <t>Alps Alpine</t>
+    <t>Mechanical Encoder Rotary Incremental Hollow 5mN.m Right Angle Quadrature Digital Square Wave 12PPR Through Hole PC Pin</t>
+  </si>
+  <si>
+    <t>Alps Electric</t>
   </si>
   <si>
     <t>THROUGH_SHAFT_ENCODER_9MM</t>
-  </si>
-  <si>
-    <t>ROHS3</t>
-  </si>
-  <si>
-    <t>https://www.digikey.ca/en/products/detail/alps-alpine/EC10E1220501/21721562</t>
   </si>
   <si>
     <t>J1</t>
@@ -557,7 +551,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{388178DE-0524-4303-8E8C-229364C24806}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F1646F2-7D08-4C84-AB15-DCB531A35312}">
   <dimension ref="A1:J7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -660,31 +654,27 @@
       <c r="H3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I3" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>21</v>
-      </c>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="D4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>25</v>
-      </c>
       <c r="F4" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G4" s="1">
         <v>1</v>
@@ -696,12 +686,12 @@
         <v>14</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>11</v>
@@ -716,7 +706,7 @@
         <v>11</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G5" s="1">
         <v>0</v>
@@ -733,22 +723,22 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="D6" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>31</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>33</v>
       </c>
       <c r="G6" s="1">
         <v>2</v>
@@ -760,27 +750,27 @@
         <v>14</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="D7" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>38</v>
-      </c>
       <c r="F7" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G7" s="1">
         <v>1</v>
@@ -792,11 +782,11 @@
         <v>14</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="258" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>